--- a/Del_1-Rapport/Test_Specifikation_Inloggningsfunktion.xlsx
+++ b/Del_1-Rapport/Test_Specifikation_Inloggningsfunktion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Studies\Testautomation_CI_CD\InlämningsUppgift_TA\Del_1-Rapport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F07E29E-5831-4DB2-9794-05E196DB4D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A9CD8B-333D-4816-8447-957368E33FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F97E49E7-5B5D-407D-92EB-A7BB87B04C5F}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F97E49E7-5B5D-407D-92EB-A7BB87B04C5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="70">
   <si>
     <t>Req ID</t>
   </si>
@@ -129,15 +129,9 @@
     <t>#2</t>
   </si>
   <si>
-    <t>def login(driver, username, password):</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Hjälpfunktion för inloggning.
  Minskar kodduplicering och gör testerna mer lättlästa.
    </t>
-  </si>
-  <si>
-    <t>Def driver():</t>
   </si>
   <si>
     <t>Fält fylls i korrekt
@@ -149,140 +143,10 @@
     <t>#3</t>
   </si>
   <si>
-    <t>def test_successful_login_username1(driver):</t>
-  </si>
-  <si>
-    <t>Användare lyckats att logga
- in med giltiga uppgifter. 
-(username: standard_user,
-password: secret_sauce)</t>
-  </si>
-  <si>
-    <t>#4</t>
-  </si>
-  <si>
-    <t>def test_successful_login_username2(driver):</t>
-  </si>
-  <si>
-    <t>Användare lyckats att logga
- in med giltiga uppgifter. 
-(username: problem_user,
-password: secret_sauce)</t>
-  </si>
-  <si>
-    <t>#5</t>
-  </si>
-  <si>
-    <t>def test_successful_login_username3(driver):</t>
-  </si>
-  <si>
-    <t>Användare lyckats att logga
- in med giltiga uppgifter. 
-(username: performance_glitch_user,
-password: secret_sauce)</t>
-  </si>
-  <si>
-    <t>#6</t>
-  </si>
-  <si>
-    <t>def test_successful_login_username4(driver):</t>
-  </si>
-  <si>
-    <t>Användare lyckats att logga
- in med giltiga uppgifter. 
-(username: error_user,
-password: secret_sauce)</t>
-  </si>
-  <si>
-    <t>Verifierar att användaren kan logga in med giltiga uppgifter.
-Detta är ett kritiskt användarflöde och lämpar sig väl för Selenium-testning.</t>
-  </si>
-  <si>
-    <t>#7</t>
-  </si>
-  <si>
-    <t>def test_successful_login_username5(driver):</t>
-  </si>
-  <si>
-    <t>Användare lyckats att logga
- in med giltiga uppgifter. 
-(username: visual_user,
-password: secret_sauce)</t>
-  </si>
-  <si>
-    <t>#8</t>
-  </si>
-  <si>
-    <t>def test_wrong_password_username1(driver):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Säkerställer att systemet blockerar inloggning vid fel lösenord
-och ger användaren korrekt feedback.
- </t>
-  </si>
-  <si>
-    <t>Användare lyckats inte att logga
- in med fel lösenord. 
-(username: standard_user,
-password: wrong_password)</t>
-  </si>
-  <si>
-    <t>#9</t>
-  </si>
-  <si>
-    <t>def test_wrong_password_username2(driver):</t>
-  </si>
-  <si>
-    <t>Säkerställer att systemet blockerar inloggning vid fel lösenord
-och ger användaren korrekt feedback.</t>
-  </si>
-  <si>
-    <t>Användare lyckats inte att logga
- in med fel lösenord. 
-(username: problem_user,
-password: wrong_password)</t>
-  </si>
-  <si>
     <t>#10</t>
   </si>
   <si>
-    <t>def test_wrong_password_username3(driver):</t>
-  </si>
-  <si>
-    <t>Användare lyckats inte att logga
- in med fel lösenord. 
-(username:  performance_glitch_user,
-password: wrong_password)</t>
-  </si>
-  <si>
-    <t>#11</t>
-  </si>
-  <si>
-    <t>def test_wrong_password_username4(driver):</t>
-  </si>
-  <si>
-    <t>Användare lyckats inte att logga
- in med fel lösenord. 
-(username:  error_user,
-password: wrong_password)</t>
-  </si>
-  <si>
-    <t>#12</t>
-  </si>
-  <si>
-    <t>def test_wrong_password_username5(driver):</t>
-  </si>
-  <si>
-    <t>Användare lyckats inte att logga
- in med fel lösenord. 
-(username:  visual_user,
-password: wrong_password)</t>
-  </si>
-  <si>
     <t>#13</t>
-  </si>
-  <si>
-    <t>def test_locked_user_givenpassword(driver):</t>
   </si>
   <si>
     <t>Låsta användare kan inte logga in. 
@@ -293,9 +157,6 @@
     <t>#14</t>
   </si>
   <si>
-    <t>def test_locked_user_wrongpassword(driver):</t>
-  </si>
-  <si>
     <t>Kontrollerar att låsta användarkonton inte kan logga in med 
 rätt lösenord, vilket är ett viktigt säkerhetskrav.</t>
   </si>
@@ -310,9 +171,6 @@
   </si>
   <si>
     <t>#15</t>
-  </si>
-  <si>
-    <t>def test_empty_fields(driver):</t>
   </si>
   <si>
     <t>Validerar att inloggning inte tillåts när obligatoriska fält saknas.</t>
@@ -327,9 +185,6 @@
     <t>#16</t>
   </si>
   <si>
-    <t>def test_username_without_password(driver):</t>
-  </si>
-  <si>
     <t>Användare kan inte logga inte med
 tömma lösenord fält.
 (username: standard_user,
@@ -339,9 +194,6 @@
     <t>#17</t>
   </si>
   <si>
-    <t>def test_password_without_username(driver):</t>
-  </si>
-  <si>
     <t>Validerar att inloggning inte tillåts när användarnamn anges
 men lösenord saknas.</t>
   </si>
@@ -391,6 +243,51 @@
   </si>
   <si>
     <t>Test specifikation &amp; Resultat- inloggningsfunktion</t>
+  </si>
+  <si>
+    <t>def page() -&gt; Page:</t>
+  </si>
+  <si>
+    <t>def login(page: Page, username: str, password: str):</t>
+  </si>
+  <si>
+    <t>def test_anvandare_kan_logga_in_med_korrekta_uppgifter(page: Page, username):</t>
+  </si>
+  <si>
+    <t>Verifierar att all användaren I pytest-dekorator pytest.mark.parametrize kan logga in med giltiga uppgifter.
+Detta är ett kritiskt användarflöde och lämpar sig väl för Selenium-testning.</t>
+  </si>
+  <si>
+    <t>def test_inloggning_misslyckas_vid_fel_losenord(page: Page, username):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verifierar att all användaren I pytest-dekorator pytest.mark.parametrize kan inte logga in med ogiltigt lösenord.
+Detta är ett kritiskt användarflöde och lämpar sig väl för Selenium-testning. </t>
+  </si>
+  <si>
+    <t>Alla användare lyckats inte att logga
+ in med fel lösenord. 
+(username: secret_sauce) I pytest-dekorator</t>
+  </si>
+  <si>
+    <t>Alla användare lyckats att logga
+ in med giltiga uppgifter. 
+(username: secret_sauce) I pytest-dekorator</t>
+  </si>
+  <si>
+    <t>def test_last_anvandare_kan_inte_logga_in_med_ratt_losenord(page: Page):</t>
+  </si>
+  <si>
+    <t>test_last_anvandare_med_fel_losenord(page: Page):</t>
+  </si>
+  <si>
+    <t>def test_inloggning_med_tomma_falt(page: Page):</t>
+  </si>
+  <si>
+    <t>def test_inloggning_med_anvandarnamn_utan_losenord(page: Page):</t>
+  </si>
+  <si>
+    <t>def test_inloggning_med_losenord_utan_anvandarnamn(page: Page):</t>
   </si>
 </sst>
 </file>
@@ -531,7 +428,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -566,50 +463,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -946,13 +837,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80BBF6A0-D8E2-406A-AD12-25A43EEED0E6}">
-  <dimension ref="A2:Q42"/>
+  <dimension ref="A2:Q28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="75.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="58.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="34.28515625" customWidth="1"/>
     <col min="8" max="8" width="22.5703125" bestFit="1" customWidth="1"/>
@@ -964,18 +855,18 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
+      <c r="A2" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
@@ -985,16 +876,16 @@
       <c r="Q2" s="6"/>
     </row>
     <row r="3" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
@@ -1004,10 +895,10 @@
       <c r="Q3" s="6"/>
     </row>
     <row r="4" spans="1:17" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="B4" s="14"/>
+      <c r="A4" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="25"/>
       <c r="C4" s="7" t="s">
         <v>8</v>
       </c>
@@ -1041,8 +932,8 @@
       <c r="Q4" s="5"/>
     </row>
     <row r="5" spans="1:17" s="1" customFormat="1" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="10" t="s">
         <v>11</v>
       </c>
@@ -1076,16 +967,16 @@
       <c r="Q5" s="5"/>
     </row>
     <row r="6" spans="1:17" ht="31.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1095,716 +986,438 @@
       <c r="Q6" s="4"/>
     </row>
     <row r="7" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="17"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="12" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>90</v>
+        <v>52</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>91</v>
+        <v>53</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="J7" s="17"/>
+        <v>54</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="24"/>
     </row>
     <row r="8" spans="1:17" ht="210" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="19" t="s">
+      <c r="B8" s="22"/>
+      <c r="C8" s="21" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>5</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="J8" s="23"/>
+      <c r="J8" s="20"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="23"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="20"/>
     </row>
     <row r="10" spans="1:17" s="2" customFormat="1" ht="120" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="19"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="21"/>
       <c r="D10" s="13" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="G10" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="H10" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="20"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="20"/>
+    </row>
+    <row r="12" spans="1:17" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J12" s="20"/>
+    </row>
+    <row r="13" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="20"/>
+    </row>
+    <row r="14" spans="1:17" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="E14" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="H14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I14" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="23"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="23"/>
-    </row>
-    <row r="12" spans="1:17" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="13" t="s">
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="22"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E18" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="H18" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="22"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="G12" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="21" t="s">
+      <c r="G24" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I24" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="23"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="23"/>
-    </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
-      <c r="B14" s="18"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="21" t="s">
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="H26" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="25" t="s">
+      <c r="I26" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="26"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="18"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="23"/>
-    </row>
-    <row r="16" spans="1:17" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="18"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J16" s="23"/>
-    </row>
-    <row r="17" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18"/>
-      <c r="B17" s="18"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="23"/>
-    </row>
-    <row r="18" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A18" s="18"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="H18" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J18" s="26"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="18"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="22"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="23"/>
-    </row>
-    <row r="20" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="18"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="21" t="s">
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="16"/>
+    </row>
+    <row r="28" spans="1:10" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="H20" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I20" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J20" s="26"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="18"/>
-      <c r="B21" s="18"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="23"/>
-    </row>
-    <row r="22" spans="1:10" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="13" t="s">
+      <c r="E28" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F28" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="G28" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="F22" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="G22" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="H22" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J22" s="23"/>
-    </row>
-    <row r="23" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="23"/>
-    </row>
-    <row r="24" spans="1:10" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="H24" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J24" s="23"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="23"/>
-    </row>
-    <row r="26" spans="1:10" s="2" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A26" s="18"/>
-      <c r="B26" s="18"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G26" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I26" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="23"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="23"/>
-    </row>
-    <row r="28" spans="1:10" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A28" s="18"/>
-      <c r="B28" s="18"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F28" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G28" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="H28" s="21" t="s">
+      <c r="H28" s="15" t="s">
         <v>23</v>
       </c>
       <c r="I28" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="J28" s="23"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="24"/>
-      <c r="G29" s="24"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="24"/>
-      <c r="J29" s="23"/>
-    </row>
-    <row r="30" spans="1:10" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="H30" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I30" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="J30" s="26"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="22"/>
-      <c r="E31" s="24"/>
-      <c r="F31" s="24"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="23"/>
-    </row>
-    <row r="32" spans="1:10" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="G32" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I32" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J32" s="23"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="23"/>
-    </row>
-    <row r="34" spans="1:10" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="G34" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I34" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J34" s="23"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="24"/>
-      <c r="F35" s="24"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="23"/>
-    </row>
-    <row r="36" spans="1:10" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="G36" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="H36" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J36" s="23"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="24"/>
-      <c r="I37" s="24"/>
-      <c r="J37" s="23"/>
-    </row>
-    <row r="38" spans="1:10" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F38" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="G38" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="H38" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I38" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J38" s="23"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="24"/>
-      <c r="H39" s="24"/>
-      <c r="I39" s="24"/>
-      <c r="J39" s="23"/>
-    </row>
-    <row r="40" spans="1:10" s="2" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F40" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G40" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="H40" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I40" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="J40" s="23"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="18"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="20"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="28"/>
-    </row>
-    <row r="42" spans="1:10" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A42" s="18"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="F42" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="G42" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H42" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I42" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J42" s="18"/>
+      <c r="J28" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="27">
     <mergeCell ref="D17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="D19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="C8:C42"/>
-    <mergeCell ref="D37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="D39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="D33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="D35:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="A2:J3"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="D15:J15"/>
-    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="A8:B28"/>
     <mergeCell ref="I7:J7"/>
     <mergeCell ref="I8:J8"/>
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="I10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="D31:J31"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="A2:J3"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="D29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="D21:J21"/>
-    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="C8:C28"/>
     <mergeCell ref="D23:J23"/>
     <mergeCell ref="I24:J24"/>
     <mergeCell ref="D25:J25"/>
-    <mergeCell ref="A8:B42"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="D19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="D21:J21"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I12:J12"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
